--- a/files/Doc_approve.xlsx
+++ b/files/Doc_approve.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bowjung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\team-file-center-main\team-file-center-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA25A07-A5F2-45AA-BCE0-7128BEF68E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1039A083-E94A-4BCD-BEF0-0C4F8145556C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="0" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
   <si>
     <t>HOME LOAN CREDIT APPROVAL</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>บาท</t>
-  </si>
-  <si>
-    <t>ระยะเวลากู้</t>
   </si>
   <si>
     <t>ปี</t>
@@ -211,6 +208,12 @@
   </si>
   <si>
     <t>เอกรัฐ  ประสานสุข</t>
+  </si>
+  <si>
+    <t>ระยะเวลากู้ HL</t>
+  </si>
+  <si>
+    <t>ระยะเวลากู้ MP</t>
   </si>
 </sst>
 </file>
@@ -786,12 +789,222 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="7" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="5" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="5" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="6" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -809,216 +1022,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="5" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="5" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="7" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1089,13 +1092,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>577454</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>168039</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1133,13 +1136,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>221456</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>36128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>783431</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>508398</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1387,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H43"/>
+  <dimension ref="B1:H44"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1410,34 +1413,34 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B2" s="96" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="98"/>
+      <c r="B2" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="37"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" ht="7.5" customHeight="1">
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="101"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="40"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="2:8" ht="12" customHeight="1">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="2:8" ht="8.1" customHeight="1">
@@ -1451,19 +1454,19 @@
     </row>
     <row r="6" spans="2:8" ht="16.5" customHeight="1">
       <c r="B6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="105" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="105"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="106">
+      <c r="F6" s="45">
         <v>46248</v>
       </c>
-      <c r="G6" s="107"/>
+      <c r="G6" s="46"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:8" ht="8.1" customHeight="1">
@@ -1476,53 +1479,53 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
-      <c r="B8" s="60" t="s">
+      <c r="B8" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="62"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="49"/>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="2:8" ht="20.25" customHeight="1">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="93" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="95"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="1"/>
     </row>
     <row r="10" spans="2:8" ht="20.25" customHeight="1">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="93" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="95"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="2:8" ht="20.25" customHeight="1">
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="90"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="54"/>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="2:8" ht="8.1" customHeight="1">
@@ -1535,429 +1538,495 @@
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="62"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="49"/>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B14" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="81">
+      <c r="B14" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="56"/>
+      <c r="D14" s="57">
         <v>5000000</v>
       </c>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
       <c r="G14" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="56"/>
+      <c r="D15" s="63">
+        <v>30</v>
+      </c>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B16" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="56"/>
+      <c r="D16" s="57">
+        <v>500000</v>
+      </c>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B17" s="62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="56"/>
+      <c r="D17" s="63">
+        <v>20</v>
+      </c>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B18" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="80"/>
-      <c r="D15" s="81">
-        <v>500000</v>
-      </c>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="7" t="s">
+      <c r="C18" s="56"/>
+      <c r="D18" s="57">
+        <v>280000</v>
+      </c>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B16" s="82" t="s">
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B19" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="66"/>
+      <c r="D19" s="67">
+        <v>15</v>
+      </c>
+      <c r="E19" s="68"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="80"/>
-      <c r="D16" s="83">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B20" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="85"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B21" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="56"/>
+      <c r="D21" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B22" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="86"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13">
+        <v>9</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B23" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="86"/>
+      <c r="D23" s="87">
+        <f>SUM(D14:F16,D18,D21)</f>
+        <v>5780030</v>
+      </c>
+      <c r="E23" s="88"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B24" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="59"/>
+      <c r="D24" s="60">
+        <v>35000</v>
+      </c>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="2:8" ht="8.1" customHeight="1">
+      <c r="B25" s="5"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B26" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="2:8" ht="15" customHeight="1">
+      <c r="B27" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B17" s="79" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="80"/>
-      <c r="D17" s="81">
-        <v>280000</v>
-      </c>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B18" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="45">
-        <v>15</v>
-      </c>
-      <c r="E18" s="46"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B19" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B20" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="80"/>
-      <c r="D20" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B21" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="49"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13">
-        <v>9</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B22" s="48" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="50">
-        <f>SUM(D14:F15,D17,D20)</f>
-        <v>5780000</v>
-      </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B23" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="76"/>
-      <c r="D23" s="77">
-        <v>35000</v>
-      </c>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B24" s="5"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B25" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
-      <c r="B26" s="66" t="s">
+      <c r="C27" s="71"/>
+      <c r="D27" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="19">
+        <v>2.79</v>
+      </c>
+      <c r="F27" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="80"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="2:8" ht="15" customHeight="1">
+      <c r="B28" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="67"/>
-      <c r="D26" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="19">
-        <v>2.79</v>
-      </c>
-      <c r="F26" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
-      <c r="B27" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="67"/>
-      <c r="D27" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="20">
-        <v>2.79</v>
-      </c>
-      <c r="F27" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="31"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
-      <c r="B28" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="67"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E28" s="20">
         <v>2.79</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" s="80"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="2:8" ht="15" customHeight="1">
+      <c r="B29" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="20">
+        <v>2.79</v>
+      </c>
+      <c r="F29" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" s="80"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="2:8" ht="15" customHeight="1">
+      <c r="B30" s="77" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="78"/>
+      <c r="D30" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="21">
+        <v>6.5250000000000004</v>
+      </c>
+      <c r="F30" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="80"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="2:8" ht="15" customHeight="1">
+      <c r="B31" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
-      <c r="B29" s="73" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="74"/>
-      <c r="D29" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="21">
-        <v>6.5250000000000004</v>
-      </c>
-      <c r="F29" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" s="31"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
-      <c r="B30" s="53" t="s">
+      <c r="C31" s="91"/>
+      <c r="D31" s="102">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="E31" s="103"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="2:8" ht="12.75" customHeight="1">
+      <c r="B32" s="72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="73"/>
+      <c r="D32" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="32">
-        <v>2.7900000000000001E-2</v>
-      </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B31" s="68" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B32" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="58"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="15" t="s">
-        <v>7</v>
-      </c>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="76"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
-      <c r="B33" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="E33" s="58"/>
-      <c r="F33" s="59"/>
+    <row r="33" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B33" s="92" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="93"/>
+      <c r="D33" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="95"/>
+      <c r="F33" s="96"/>
       <c r="G33" s="15" t="s">
         <v>7</v>
       </c>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B34" s="5"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="6"/>
+    <row r="34" spans="2:8" ht="15" customHeight="1">
+      <c r="B34" s="92" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="93"/>
+      <c r="D34" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="95"/>
+      <c r="F34" s="96"/>
+      <c r="G34" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B35" s="60" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="62"/>
+    <row r="35" spans="2:8" ht="8.1" customHeight="1">
+      <c r="B35" s="5"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="2:8" ht="17.25" customHeight="1">
-      <c r="B36" s="26" t="str">
+    <row r="36" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B36" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="2:8" ht="17.25" customHeight="1">
+      <c r="B37" s="26" t="str">
         <f>_xlfn.UNICHAR(9745)</f>
         <v>☑</v>
       </c>
-      <c r="C36" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="26" t="str">
+      <c r="C37" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="26" t="str">
         <f>_xlfn.UNICHAR(9744)</f>
         <v>☐</v>
       </c>
-      <c r="E36" s="34" t="s">
+      <c r="E37" s="104" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" s="105"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="2:8" ht="19.5" hidden="1" customHeight="1">
+      <c r="B38" s="23"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="2:8" ht="8.1" customHeight="1">
+      <c r="B39" s="5"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="2:8" ht="15" customHeight="1">
+      <c r="B40" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="98"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="98"/>
+      <c r="G40" s="99"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="2:8" ht="43.5" customHeight="1">
+      <c r="B41" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="106" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="106"/>
+      <c r="E41" s="100" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="100"/>
+      <c r="G41" s="101"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="2:8" ht="15.75" customHeight="1">
+      <c r="B42" s="29"/>
+      <c r="C42" s="107" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="100"/>
+      <c r="E42" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="35"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="2:8" ht="19.5" hidden="1" customHeight="1">
-      <c r="B37" s="23"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B38" s="5"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
-      <c r="B39" s="63" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="64"/>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="64"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="2:8" ht="43.5" customHeight="1">
-      <c r="B40" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="38" t="s">
+      <c r="F42" s="100"/>
+      <c r="G42" s="101"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="2:8" ht="24" customHeight="1">
+      <c r="B43" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="38"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B41" s="29"/>
-      <c r="C41" s="37" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="38"/>
-      <c r="E41" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="F41" s="38"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="2:8" ht="24" customHeight="1">
-      <c r="B42" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" s="41"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="82"/>
+      <c r="G43" s="83"/>
       <c r="H43" s="1"/>
     </row>
+    <row r="44" spans="2:8" ht="8.1" customHeight="1">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="60">
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="B10:C10"/>
@@ -1967,55 +2036,6 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:G41"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/files/Doc_approve.xlsx
+++ b/files/Doc_approve.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\team-file-center-main\team-file-center-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1039A083-E94A-4BCD-BEF0-0C4F8145556C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E63E2AA-8590-4BB7-803B-33F093EB38EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="0" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="53">
   <si>
     <t>HOME LOAN CREDIT APPROVAL</t>
   </si>
@@ -69,9 +69,6 @@
     <t>ผลการพิจารณา</t>
   </si>
   <si>
-    <t>ผู้จัดทำ / ผู้เสนอ</t>
-  </si>
-  <si>
     <t>ผู้มีอำนาจอนุมัติ</t>
   </si>
   <si>
@@ -94,12 +91,6 @@
   </si>
   <si>
     <t>วงเงินที่กู้  MP</t>
-  </si>
-  <si>
-    <t>ประกันคุ้มครองวงเงินกู้</t>
-  </si>
-  <si>
-    <t>ระยะเวลาคุ้มครอง</t>
   </si>
   <si>
     <r>
@@ -210,10 +201,16 @@
     <t>เอกรัฐ  ประสานสุข</t>
   </si>
   <si>
-    <t>ระยะเวลากู้ HL</t>
-  </si>
-  <si>
-    <t>ระยะเวลากู้ MP</t>
+    <t>ประกันคุ้มครองวงเงินกู้ HL</t>
+  </si>
+  <si>
+    <t>ระยะเวลากู้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   ผู้จัดทำ / ผู้เสนอ</t>
+  </si>
+  <si>
+    <t>คุ้มครอง</t>
   </si>
 </sst>
 </file>
@@ -226,7 +223,7 @@
     <numFmt numFmtId="188" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="189" formatCode="0.000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -297,8 +294,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,6 +340,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="28">
     <border>
@@ -700,7 +714,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -747,23 +761,11 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="4" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="189" fontId="7" fillId="4" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -789,6 +791,183 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="5" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="5" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="7" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -831,197 +1010,87 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="187" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="187" fontId="1" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="7" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="5" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="13" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="1" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="189" fontId="7" fillId="9" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="7" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="5" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="5" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="1" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1092,13 +1161,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>104776</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>577454</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>606761</xdr:colOff>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>168039</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1134,15 +1203,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>221456</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>36128</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>783431</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>508398</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1390,20 +1459,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H44"/>
+  <dimension ref="B1:I43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="11.25" customWidth="1"/>
     <col min="3" max="3" width="16.375" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="9.875" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="8.75" customWidth="1"/>
-    <col min="8" max="8" width="4" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="3.625" customWidth="1"/>
+    <col min="6" max="6" width="9.875" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="8.75" customWidth="1"/>
+    <col min="9" max="9" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="8.1" customHeight="1">
+    <row r="1" spans="2:9" ht="8.1" customHeight="1">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1411,631 +1481,671 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B2" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" ht="7.5" customHeight="1">
-      <c r="B3" s="38"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="2:8" ht="12" customHeight="1">
-      <c r="B4" s="41" t="s">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="2:9" ht="13.5" customHeight="1">
+      <c r="B2" s="90" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" ht="7.5" customHeight="1">
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="2:9" ht="12" customHeight="1">
+      <c r="B4" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="2:8" ht="8.1" customHeight="1">
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="2:9" ht="8.1" customHeight="1">
       <c r="B5" s="3"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B6" s="17" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44"/>
-      <c r="E6" s="9" t="s">
+      <c r="D6" s="109"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="45">
+      <c r="G6" s="99">
         <v>46248</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="2:8" ht="8.1" customHeight="1">
+      <c r="H6" s="100"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="2:9" ht="8.1" customHeight="1">
       <c r="B7" s="5"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
-      <c r="B8" s="47" t="s">
+      <c r="G7" s="2"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="2:9" ht="15" customHeight="1">
+      <c r="B8" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="2:8" ht="20.25" customHeight="1">
-      <c r="B9" s="30" t="s">
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B9" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="2:8" ht="20.25" customHeight="1">
-      <c r="B10" s="30" t="s">
+      <c r="C9" s="86"/>
+      <c r="D9" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="101"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B10" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="2:8" ht="20.25" customHeight="1">
-      <c r="B11" s="50" t="s">
+      <c r="C10" s="86"/>
+      <c r="D10" s="87" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="101"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="89"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B11" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="2:8" ht="8.1" customHeight="1">
+      <c r="C11" s="81"/>
+      <c r="D11" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="82"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="2:9" ht="8.1" customHeight="1">
       <c r="B12" s="5"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B13" s="47" t="s">
+      <c r="G12" s="2"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B13" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B14" s="55" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B14" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="63"/>
+      <c r="D14" s="118">
+        <v>5000000</v>
+      </c>
+      <c r="E14" s="112" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="111" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="114">
+        <v>30</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B15" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="63"/>
+      <c r="D15" s="118">
+        <v>495000</v>
+      </c>
+      <c r="E15" s="113" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="111" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="115">
+        <v>30</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B16" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57">
-        <v>5000000</v>
-      </c>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="7" t="s">
+      <c r="C16" s="63"/>
+      <c r="D16" s="118">
+        <v>500000</v>
+      </c>
+      <c r="E16" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B15" s="62" t="s">
+      <c r="F16" s="111" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="116">
+        <v>20</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B17" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="63"/>
+      <c r="D17" s="118">
+        <v>25000</v>
+      </c>
+      <c r="E17" s="112" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="111" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="56"/>
-      <c r="D15" s="63">
+      <c r="G17" s="117">
+        <v>20</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B18" s="62"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B19" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B20" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="103"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B21" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="46"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13">
+        <v>9</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B22" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="46"/>
+      <c r="D22" s="47">
+        <f>SUM(D14:G16,D18,D20)</f>
+        <v>5995080</v>
+      </c>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B23" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="74"/>
+      <c r="D23" s="75">
+        <v>35000</v>
+      </c>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="2:9" ht="8.1" customHeight="1">
+      <c r="B24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B25" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="2:9" ht="15" customHeight="1">
+      <c r="B26" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="63"/>
+      <c r="D26" s="119" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="120"/>
+      <c r="F26" s="121">
+        <v>2.79</v>
+      </c>
+      <c r="G26" s="125" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="126"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="2:9" ht="15" customHeight="1">
+      <c r="B27" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="63"/>
+      <c r="D27" s="119" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="122"/>
+      <c r="F27" s="123">
+        <v>2.79</v>
+      </c>
+      <c r="G27" s="125" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="126"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="2:9" ht="15" customHeight="1">
+      <c r="B28" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="63"/>
+      <c r="D28" s="119" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="122"/>
+      <c r="F28" s="123">
+        <v>2.79</v>
+      </c>
+      <c r="G28" s="125" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="126"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="2:9" ht="15" customHeight="1">
+      <c r="B29" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="70"/>
+      <c r="D29" s="120" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="120"/>
+      <c r="F29" s="124">
+        <v>6.5250000000000004</v>
+      </c>
+      <c r="G29" s="125" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" s="126"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="2:9" ht="15" customHeight="1">
+      <c r="B30" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="51"/>
+      <c r="D30" s="71">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="E30" s="104"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="2:9" ht="12.75" customHeight="1">
+      <c r="B31" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="65"/>
+      <c r="D31" s="66" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="105"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B32" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B16" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="56"/>
-      <c r="D16" s="57">
-        <v>500000</v>
-      </c>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="7" t="s">
+      <c r="C32" s="53"/>
+      <c r="D32" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="106"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B17" s="62" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="63">
-        <v>20</v>
-      </c>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B18" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57">
-        <v>280000</v>
-      </c>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="7" t="s">
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="2:9" ht="15" customHeight="1">
+      <c r="B33" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="53"/>
+      <c r="D33" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="106"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B19" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="66"/>
-      <c r="D19" s="67">
-        <v>15</v>
-      </c>
-      <c r="E19" s="68"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B20" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="85"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="69"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B21" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="57"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B22" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13">
-        <v>9</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B23" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="86"/>
-      <c r="D23" s="87">
-        <f>SUM(D14:F16,D18,D21)</f>
-        <v>5780030</v>
-      </c>
-      <c r="E23" s="88"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B24" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="59"/>
-      <c r="D24" s="60">
-        <v>35000</v>
-      </c>
-      <c r="E24" s="60"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B25" s="5"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B26" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
-      <c r="B27" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="19">
-        <v>2.79</v>
-      </c>
-      <c r="F27" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27" s="80"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
-      <c r="B28" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="71"/>
-      <c r="D28" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="20">
-        <v>2.79</v>
-      </c>
-      <c r="F28" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" s="80"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
-      <c r="B29" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="20">
-        <v>2.79</v>
-      </c>
-      <c r="F29" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" s="80"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
-      <c r="B30" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="78"/>
-      <c r="D30" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="21">
-        <v>6.5250000000000004</v>
-      </c>
-      <c r="F30" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="80"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
-      <c r="B31" s="90" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="91"/>
-      <c r="D31" s="102">
-        <v>2.7900000000000001E-2</v>
-      </c>
-      <c r="E31" s="103"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="2:8" ht="12.75" customHeight="1">
-      <c r="B32" s="72" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="73"/>
-      <c r="D32" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B33" s="92" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="93"/>
-      <c r="D33" s="94" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" s="95"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
-      <c r="B34" s="92" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="93"/>
-      <c r="D34" s="94" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="95"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B35" s="5"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B36" s="47" t="s">
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="2:9" ht="8.1" customHeight="1">
+      <c r="B34" s="5"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B35" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="2:8" ht="17.25" customHeight="1">
-      <c r="B37" s="26" t="str">
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="2:9" ht="17.25" customHeight="1">
+      <c r="B36" s="22" t="str">
         <f>_xlfn.UNICHAR(9745)</f>
         <v>☑</v>
       </c>
-      <c r="C37" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="26" t="str">
+      <c r="C36" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="22"/>
+      <c r="E36" s="107" t="str">
         <f>_xlfn.UNICHAR(9744)</f>
         <v>☐</v>
       </c>
-      <c r="E37" s="104" t="s">
+      <c r="F36" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" s="31"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="2:9" ht="19.5" hidden="1" customHeight="1">
+      <c r="B37" s="19"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="2:9" ht="8.1" customHeight="1">
+      <c r="B38" s="5"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="2:9" ht="15" customHeight="1">
+      <c r="B39" s="110" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="60"/>
+      <c r="H39" s="61"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="2:9" ht="43.5" customHeight="1">
+      <c r="B40" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F37" s="105"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="2:8" ht="19.5" hidden="1" customHeight="1">
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B39" s="5"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
-      <c r="B40" s="97" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="98"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98" t="s">
+      <c r="C40" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="32"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="98"/>
-      <c r="G40" s="99"/>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="2:8" ht="43.5" customHeight="1">
-      <c r="B41" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C41" s="106" t="s">
-        <v>51</v>
-      </c>
-      <c r="D41" s="106"/>
-      <c r="E41" s="100" t="s">
+      <c r="G40" s="34"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="2:9" ht="15.75" customHeight="1">
+      <c r="B41" s="25"/>
+      <c r="C41" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="34"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="34"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="2:9" ht="24" customHeight="1">
+      <c r="B42" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="100"/>
-      <c r="G41" s="101"/>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="2:8" ht="15.75" customHeight="1">
-      <c r="B42" s="29"/>
-      <c r="C42" s="107" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="100"/>
-      <c r="E42" s="107" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="100"/>
-      <c r="G42" s="101"/>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="2:8" ht="24" customHeight="1">
-      <c r="B43" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="82"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="82"/>
-      <c r="G43" s="83"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="38"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="2:9" ht="8.1" customHeight="1">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="2:8" ht="8.1" customHeight="1">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
+      <c r="I43" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="E37:F37"/>
+  <mergeCells count="54">
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:G32"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="B2:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
